--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2995,6 +2995,27 @@
       </c>
       <c r="E123" s="7">
         <f>C123-C122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1659</v>
+      </c>
+      <c r="C124" t="n">
+        <v>5990</v>
+      </c>
+      <c r="D124" s="7">
+        <f>B124-B123</f>
+        <v/>
+      </c>
+      <c r="E124" s="7">
+        <f>C124-C123</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3016,6 +3016,27 @@
       </c>
       <c r="E124" s="7">
         <f>C124-C123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1660</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D125" s="7">
+        <f>B125-B124</f>
+        <v/>
+      </c>
+      <c r="E125" s="7">
+        <f>C125-C124</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3037,6 +3037,27 @@
       </c>
       <c r="E125" s="7">
         <f>C125-C124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D126" s="7">
+        <f>B126-B125</f>
+        <v/>
+      </c>
+      <c r="E126" s="7">
+        <f>C126-C125</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3058,6 +3058,27 @@
       </c>
       <c r="E126" s="7">
         <f>C126-C125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6010</v>
+      </c>
+      <c r="D127" s="7">
+        <f>B127-B126</f>
+        <v/>
+      </c>
+      <c r="E127" s="7">
+        <f>C127-C126</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3079,6 +3079,27 @@
       </c>
       <c r="E127" s="7">
         <f>C127-C126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1665</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6020</v>
+      </c>
+      <c r="D128" s="7">
+        <f>B128-B127</f>
+        <v/>
+      </c>
+      <c r="E128" s="7">
+        <f>C128-C127</f>
         <v/>
       </c>
     </row>

--- a/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
+++ b/03_projects/MONOQROME/monoqrome_sns_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3100,6 +3100,27 @@
       </c>
       <c r="E128" s="7">
         <f>C128-C127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1666</v>
+      </c>
+      <c r="C129" t="n">
+        <v>6020</v>
+      </c>
+      <c r="D129" s="7">
+        <f>B129-B128</f>
+        <v/>
+      </c>
+      <c r="E129" s="7">
+        <f>C129-C128</f>
         <v/>
       </c>
     </row>
